--- a/outputs/42515.xlsx
+++ b/outputs/42515.xlsx
@@ -158,32 +158,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -439,384 +443,384 @@
   <dimension ref="A3:G19"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.66"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1.744944</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="2" t="str">
+      <c r="C5" s="6" t="n">
+        <v>44743</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A5,3)</f>
         <v>EUR-AUD</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <f aca="false">SUM(1/((1/B5)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C5)))</f>
+      <c r="F5" s="7" t="n">
+        <f aca="false">SUM(1/((1/B5)*INDEX($B$5:$B$19,MATCH(C5,$C$5:$C$19,0)+3)))</f>
         <v>1.49283288889117</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>1.171316</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="2" t="str">
+      <c r="C6" s="6" t="n">
+        <v>44743</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A6,3)</f>
         <v>EUR-CHF</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <f aca="false">SUM(1/((1/B6)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C6)))</f>
+      <c r="F6" s="7" t="n">
+        <f aca="false">SUM(1/((1/B6)*INDEX($B$5:$B$19,MATCH(C6,$C$5:$C$19,0)+3)))</f>
         <v>1.00208318896449</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>1.031269</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="2" t="str">
+      <c r="C7" s="6" t="n">
+        <v>44743</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A7,3)</f>
         <v>EUR-USD</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <f aca="false">SUM(1/((1/B7)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C7)))</f>
+      <c r="F7" s="7" t="n">
+        <f aca="false">SUM(1/((1/B7)*INDEX($B$5:$B$19,MATCH(C7,$C$5:$C$19,0)+3)))</f>
         <v>0.882270308098087</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>1.168881</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="2" t="str">
+      <c r="C8" s="6" t="n">
+        <v>44743</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A8,3)</f>
         <v>EUR-EUR</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <f aca="false">SUM(1/((1/B8)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C8)))</f>
+      <c r="F8" s="7" t="n">
+        <f aca="false">SUM(1/((1/B8)*INDEX($B$5:$B$19,MATCH(C8,$C$5:$C$19,0)+3)))</f>
         <v>1</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>20.278341</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>44743</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="2" t="str">
+      <c r="C9" s="6" t="n">
+        <v>44743</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A9,3)</f>
         <v>EUR-ZAR</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <f aca="false">SUM(1/((1/B9)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C9)))</f>
+      <c r="F9" s="7" t="n">
+        <f aca="false">SUM(1/((1/B9)*INDEX($B$5:$B$19,MATCH(C9,$C$5:$C$19,0)+3)))</f>
         <v>17.3485076752894</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>1.739228</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>44746</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="2" t="str">
+      <c r="C10" s="6" t="n">
+        <v>44746</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A10,3)</f>
         <v>EUR-AUD</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <f aca="false">SUM(1/((1/B10)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C10)))</f>
+      <c r="F10" s="7" t="n">
+        <f aca="false">SUM(1/((1/B10)*INDEX($B$5:$B$19,MATCH(C10,$C$5:$C$19,0)+3)))</f>
         <v>1.48796820152268</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>44746</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>1.337483</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>44746</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="2" t="str">
+      <c r="C11" s="6" t="n">
+        <v>44746</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A11,3)</f>
         <v>EUR-CHF</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <f aca="false">SUM(1/((1/B11)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C11)))</f>
+      <c r="F11" s="7" t="n">
+        <f aca="false">SUM(1/((1/B11)*INDEX($B$5:$B$19,MATCH(C11,$C$5:$C$19,0)+3)))</f>
         <v>1.14426180700699</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>44746</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1.225266</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>44746</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="2" t="str">
+      <c r="C12" s="6" t="n">
+        <v>44746</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A12,3)</f>
         <v>EUR-USD</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <f aca="false">SUM(1/((1/B12)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C12)))</f>
+      <c r="F12" s="7" t="n">
+        <f aca="false">SUM(1/((1/B12)*INDEX($B$5:$B$19,MATCH(C12,$C$5:$C$19,0)+3)))</f>
         <v>1.04825637950107</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>44746</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>1.168861</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>44746</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="2" t="str">
+      <c r="C13" s="6" t="n">
+        <v>44746</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A13,3)</f>
         <v>EUR-EUR</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <f aca="false">SUM(1/((1/B13)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C13)))</f>
+      <c r="F13" s="7" t="n">
+        <f aca="false">SUM(1/((1/B13)*INDEX($B$5:$B$19,MATCH(C13,$C$5:$C$19,0)+3)))</f>
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>44746</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>19.26335</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>44746</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="2" t="str">
+      <c r="C14" s="6" t="n">
+        <v>44746</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A14,3)</f>
         <v>EUR-ZAR</v>
       </c>
-      <c r="F14" s="6" t="n">
-        <f aca="false">SUM(1/((1/B14)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C14)))</f>
+      <c r="F14" s="7" t="n">
+        <f aca="false">SUM(1/((1/B14)*INDEX($B$5:$B$19,MATCH(C14,$C$5:$C$19,0)+3)))</f>
         <v>16.4804454935189</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>44746</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1.904353</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>44747</v>
-      </c>
-      <c r="E15" s="2" t="str">
+      <c r="C15" s="6" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E15" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A15,3)</f>
         <v>EUR-AUD</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <f aca="false">SUM(1/((1/B15)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C15)))</f>
+      <c r="F15" s="7" t="n">
+        <f aca="false">SUM(1/((1/B15)*INDEX($B$5:$B$19,MATCH(C15,$C$5:$C$19,0)+3)))</f>
         <v>1.45888082295044</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>44747</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>1.227956</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>44747</v>
-      </c>
-      <c r="E16" s="2" t="str">
+      <c r="C16" s="6" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E16" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A16,3)</f>
         <v>EUR-CHF</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <f aca="false">SUM(1/((1/B16)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C16)))</f>
+      <c r="F16" s="7" t="n">
+        <f aca="false">SUM(1/((1/B16)*INDEX($B$5:$B$19,MATCH(C16,$C$5:$C$19,0)+3)))</f>
         <v>0.940708713052112</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>44747</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>1.103597</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>44747</v>
-      </c>
-      <c r="E17" s="2" t="str">
+      <c r="C17" s="6" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E17" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A17,3)</f>
         <v>EUR-USD</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <f aca="false">SUM(1/((1/B17)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C17)))</f>
+      <c r="F17" s="7" t="n">
+        <f aca="false">SUM(1/((1/B17)*INDEX($B$5:$B$19,MATCH(C17,$C$5:$C$19,0)+3)))</f>
         <v>0.845440157137692</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>44747</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>1.305352</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>44747</v>
-      </c>
-      <c r="E18" s="2" t="str">
+      <c r="C18" s="6" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E18" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A18,3)</f>
         <v>EUR-EUR</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <f aca="false">SUM(1/((1/B18)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C18)))</f>
+      <c r="F18" s="7" t="n">
+        <f aca="false">SUM(1/((1/B18)*INDEX($B$5:$B$19,MATCH(C18,$C$5:$C$19,0)+3)))</f>
         <v>1</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <v>44747</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>20.898943</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>44747</v>
-      </c>
-      <c r="E19" s="2" t="str">
+      <c r="C19" s="6" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E19" s="3" t="str">
         <f aca="false">"EUR"&amp;"-"&amp;RIGHT($A19,3)</f>
         <v>EUR-ZAR</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <f aca="false">SUM(1/((1/B19)*SUMIFS($B$5:$B$19,$A$5:$A$19,"GBP-EUR",$C$5:$C$19,C19)))</f>
+      <c r="F19" s="7" t="n">
+        <f aca="false">SUM(1/((1/B19)*INDEX($B$5:$B$19,MATCH(C19,$C$5:$C$19,0)+3)))</f>
         <v>16.0101972494775</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>44747</v>
       </c>
     </row>
